--- a/data/trans_dic/IP16A08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,41</t>
+          <t>0,0; 14,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,92</t>
+          <t>0,0; 12,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,77</t>
+          <t>0,0; 13,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 24,56</t>
+          <t>4,52; 25,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>0,0; 9,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 21,94</t>
+          <t>2,7; 22,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,55</t>
+          <t>2,63; 14,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,75</t>
+          <t>0,76; 8,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,27</t>
+          <t>2,46; 13,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 26,73</t>
+          <t>7,73; 27,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 18,42</t>
+          <t>3,73; 17,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 15,27</t>
+          <t>1,31; 14,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 16,53</t>
+          <t>2,56; 16,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 19,37</t>
+          <t>5,5; 20,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 15,17</t>
+          <t>3,88; 14,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 24,02</t>
+          <t>5,53; 23,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 24,0</t>
+          <t>5,16; 23,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 20,47</t>
+          <t>8,05; 20,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 13,59</t>
+          <t>4,79; 14,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,71</t>
+          <t>4,46; 15,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 17,35</t>
+          <t>5,52; 17,22</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 42,21</t>
+          <t>11,71; 41,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 33,82</t>
+          <t>8,57; 32,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,79; 37,42</t>
+          <t>14,13; 38,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 28,44</t>
+          <t>8,21; 28,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 37,01</t>
+          <t>9,77; 37,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 44,57</t>
+          <t>16,05; 44,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 31,22</t>
+          <t>8,7; 32,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 22,12</t>
+          <t>4,52; 21,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,23; 33,9</t>
+          <t>14,61; 34,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 34,18</t>
+          <t>15,24; 33,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 30,7</t>
+          <t>14,38; 30,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 20,59</t>
+          <t>6,74; 20,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 35,78</t>
+          <t>11,06; 33,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 36,53</t>
+          <t>12,35; 38,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 40,93</t>
+          <t>10,45; 43,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 15,6</t>
+          <t>1,98; 17,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,19; 35,47</t>
+          <t>13,76; 35,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 41,6</t>
+          <t>11,93; 39,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 36,47</t>
+          <t>9,52; 38,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 20,91</t>
+          <t>5,63; 20,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 30,29</t>
+          <t>14,49; 30,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 34,05</t>
+          <t>14,66; 34,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,19; 33,2</t>
+          <t>12,08; 33,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,35</t>
+          <t>4,48; 14,68</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 22,33</t>
+          <t>10,7; 21,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 17,45</t>
+          <t>8,13; 17,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 19,74</t>
+          <t>9,4; 19,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,78</t>
+          <t>4,38; 13,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 21,39</t>
+          <t>11,84; 21,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,5</t>
+          <t>8,43; 17,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,01</t>
+          <t>9,65; 20,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,2</t>
+          <t>6,51; 15,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 19,96</t>
+          <t>12,68; 19,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,14</t>
+          <t>9,35; 15,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,7</t>
+          <t>10,78; 18,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,44</t>
+          <t>6,3; 12,63</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3642</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4229</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4737</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3736</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1340; 7604</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>647; 5428</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1546; 8591</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>567; 6339</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1256; 6666</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6734</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5605</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12339</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10234</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7734</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9773</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3342; 12024</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2003; 9575</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>552; 6200</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1195; 7819</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2801; 10277</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2592; 9846</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2385; 10037</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2526; 11317</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7579; 19433</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5764; 16872</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3809; 13144</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5273; 16465</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8734</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5577</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7942</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10808</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13477</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15082</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10578</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2635; 9396</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2559; 9609</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5104; 13884</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3049; 10531</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2332; 8886</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4479; 12455</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2910; 10924</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2086; 9977</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6777; 16146</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8809; 19525</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10001; 21548</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5618; 16805</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5310</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5826</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8998</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15277</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12217</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13244</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3377; 10158</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3354; 10481</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2307; 9571</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1540; 13350</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5427; 13836</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2967; 9908</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2165; 8781</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3639; 13487</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10139; 21356</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7627; 18064</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5416; 15221</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6385; 20946</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17758</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17623</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>18609</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>42776</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13412; 26859</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11969; 25357</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11976; 25387</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7776; 23123</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17037; 31549</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13322; 27433</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11902; 25702</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11853; 27454</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>34147; 53489</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>28536; 47421</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>27028; 45709</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>22666; 45449</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Edad-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,56</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,98</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,82</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 25,64</t>
+          <t>4,42; 24,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,34</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 22,64</t>
+          <t>2,68; 24,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 14,64</t>
+          <t>2,83; 15,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,46</t>
+          <t>0,75; 6,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,07</t>
+          <t>2,34; 13,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 27,82</t>
+          <t>8,31; 28,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 17,83</t>
+          <t>4,03; 18,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,68</t>
+          <t>1,31; 16,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 16,77</t>
+          <t>2,76; 16,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 20,17</t>
+          <t>5,2; 20,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 14,75</t>
+          <t>3,94; 14,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 23,29</t>
+          <t>5,01; 22,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 23,1</t>
+          <t>6,27; 25,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 20,63</t>
+          <t>8,02; 19,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 14,01</t>
+          <t>4,91; 13,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 15,4</t>
+          <t>4,88; 15,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 17,22</t>
+          <t>5,52; 16,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 41,75</t>
+          <t>11,99; 43,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 32,17</t>
+          <t>8,43; 32,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 38,43</t>
+          <t>13,8; 37,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 28,35</t>
+          <t>6,47; 26,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 37,23</t>
+          <t>10,27; 37,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,05; 44,62</t>
+          <t>15,1; 45,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 32,66</t>
+          <t>9,07; 33,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 21,61</t>
+          <t>4,22; 21,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,61; 34,82</t>
+          <t>14,29; 34,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,24; 33,79</t>
+          <t>14,66; 33,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 30,97</t>
+          <t>14,53; 31,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 20,17</t>
+          <t>7,5; 20,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 33,26</t>
+          <t>10,03; 34,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 38,58</t>
+          <t>12,16; 39,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 43,38</t>
+          <t>12,09; 43,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 17,12</t>
+          <t>1,86; 16,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 35,08</t>
+          <t>13,35; 36,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 39,84</t>
+          <t>11,35; 39,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,52; 38,58</t>
+          <t>9,22; 36,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 20,85</t>
+          <t>5,31; 20,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 30,52</t>
+          <t>15,01; 31,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 34,71</t>
+          <t>14,07; 34,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,08; 33,96</t>
+          <t>12,94; 34,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 14,68</t>
+          <t>4,56; 15,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 21,43</t>
+          <t>10,34; 21,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,22</t>
+          <t>8,3; 17,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 19,92</t>
+          <t>9,27; 19,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,01</t>
+          <t>4,38; 12,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 21,92</t>
+          <t>11,59; 21,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,37</t>
+          <t>8,94; 18,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 20,85</t>
+          <t>9,82; 20,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,07</t>
+          <t>6,53; 15,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 19,87</t>
+          <t>12,26; 19,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,54</t>
+          <t>9,49; 15,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 18,23</t>
+          <t>10,9; 18,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,63</t>
+          <t>6,62; 12,52</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 3283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4737</t>
+          <t>0; 3866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3736</t>
+          <t>0; 3795</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1340; 7604</t>
+          <t>1310; 7392</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 2648</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>647; 5428</t>
+          <t>644; 5838</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1546; 8591</t>
+          <t>1660; 8982</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>567; 6339</t>
+          <t>565; 4581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1256; 6666</t>
+          <t>1195; 6994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3342; 12024</t>
+          <t>3591; 12419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2003; 9575</t>
+          <t>2164; 9907</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>552; 6200</t>
+          <t>555; 7028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1195; 7819</t>
+          <t>1289; 7778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2801; 10277</t>
+          <t>2650; 10197</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2592; 9846</t>
+          <t>2632; 9999</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2385; 10037</t>
+          <t>2160; 9776</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2526; 11317</t>
+          <t>3072; 12514</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7579; 19433</t>
+          <t>7556; 18735</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5764; 16872</t>
+          <t>5919; 16067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3809; 13144</t>
+          <t>4161; 13203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5273; 16465</t>
+          <t>5273; 16095</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2635; 9396</t>
+          <t>2698; 9884</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2559; 9609</t>
+          <t>2517; 9645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5104; 13884</t>
+          <t>4985; 13412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3049; 10531</t>
+          <t>2403; 10019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2332; 8886</t>
+          <t>2451; 9018</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4479; 12455</t>
+          <t>4216; 12766</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2910; 10924</t>
+          <t>3034; 11286</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2086; 9977</t>
+          <t>1948; 10056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6777; 16146</t>
+          <t>6627; 16191</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8809; 19525</t>
+          <t>8470; 19574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10001; 21548</t>
+          <t>10112; 21598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5618; 16805</t>
+          <t>6249; 17039</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3377; 10158</t>
+          <t>3062; 10644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3354; 10481</t>
+          <t>3304; 10807</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2307; 9571</t>
+          <t>2668; 9490</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1540; 13350</t>
+          <t>1452; 12613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5427; 13836</t>
+          <t>5266; 14489</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2967; 9908</t>
+          <t>2824; 9904</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2165; 8781</t>
+          <t>2098; 8280</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3639; 13487</t>
+          <t>3438; 13218</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10139; 21356</t>
+          <t>10504; 22283</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7627; 18064</t>
+          <t>7322; 17982</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5416; 15221</t>
+          <t>5800; 15420</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6385; 20946</t>
+          <t>6507; 21811</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13412; 26859</t>
+          <t>12958; 26910</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11969; 25357</t>
+          <t>12225; 25543</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11976; 25387</t>
+          <t>11815; 24797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7776; 23123</t>
+          <t>7779; 22522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17037; 31549</t>
+          <t>16676; 31017</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13322; 27433</t>
+          <t>14124; 28594</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11902; 25702</t>
+          <t>12105; 25464</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11853; 27454</t>
+          <t>11891; 27497</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34147; 53489</t>
+          <t>32995; 52511</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28536; 47421</t>
+          <t>28961; 47480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27028; 45709</t>
+          <t>27336; 45555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22666; 45449</t>
+          <t>23828; 45074</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,37 +649,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,34%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>4,85; 24,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,59</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,04</t>
+          <t>2,65; 21,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 24,93</t>
+          <t>0,0; 14,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 11,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 24,35</t>
+          <t>0,0; 14,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,3</t>
+          <t>2,83; 14,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,11</t>
+          <t>0,75; 6,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,71</t>
+          <t>2,48; 13,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,36%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>15,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 28,73</t>
+          <t>5,38; 19,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 18,45</t>
+          <t>3,98; 15,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 16,64</t>
+          <t>5,39; 24,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 16,68</t>
+          <t>5,08; 20,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 20,01</t>
+          <t>8,25; 26,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,98</t>
+          <t>4,01; 18,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 22,69</t>
+          <t>1,33; 15,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 25,55</t>
+          <t>3,42; 18,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 19,89</t>
+          <t>8,35; 20,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,34</t>
+          <t>4,94; 13,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 15,47</t>
+          <t>5,0; 15,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 16,83</t>
+          <t>5,65; 16,38</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21,65%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>25,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>24,18%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 43,91</t>
+          <t>10,77; 37,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 32,29</t>
+          <t>15,87; 44,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 37,13</t>
+          <t>10,25; 31,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 26,97</t>
+          <t>4,51; 23,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 37,79</t>
+          <t>12,68; 42,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 45,73</t>
+          <t>7,62; 33,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 33,74</t>
+          <t>13,79; 37,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 21,78</t>
+          <t>6,8; 28,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 34,91</t>
+          <t>14,23; 33,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 33,87</t>
+          <t>15,1; 34,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 31,04</t>
+          <t>13,8; 30,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 20,45</t>
+          <t>7,36; 21,37</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20,56%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>24,06%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 34,85</t>
+          <t>14,19; 35,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,16; 39,78</t>
+          <t>11,46; 41,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 43,01</t>
+          <t>9,4; 36,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 16,18</t>
+          <t>6,04; 22,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 36,74</t>
+          <t>10,57; 35,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 39,83</t>
+          <t>12,05; 36,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 36,38</t>
+          <t>9,9; 40,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 20,43</t>
+          <t>5,59; 22,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 31,84</t>
+          <t>15,02; 30,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 34,56</t>
+          <t>14,32; 34,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 34,4</t>
+          <t>12,19; 33,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 15,29</t>
+          <t>7,06; 18,58</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,48</t>
+          <t>11,61; 21,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,35</t>
+          <t>8,66; 17,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 19,45</t>
+          <t>10,39; 21,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,67</t>
+          <t>6,71; 15,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 21,55</t>
+          <t>10,94; 22,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,1</t>
+          <t>8,09; 17,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,66</t>
+          <t>9,42; 19,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 15,09</t>
+          <t>6,81; 16,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,26; 19,5</t>
+          <t>12,64; 19,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,56</t>
+          <t>9,27; 16,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 18,17</t>
+          <t>11,03; 19,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,52</t>
+          <t>7,77; 13,8</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,37 +1577,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1174</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>1439; 7283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3866</t>
+          <t>0; 3319</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3795</t>
+          <t>635; 5259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1310; 7392</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2648</t>
+          <t>0; 4350</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>644; 5838</t>
+          <t>0; 3994</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1660; 8982</t>
+          <t>1662; 8540</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>565; 4581</t>
+          <t>563; 5056</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1195; 6994</t>
+          <t>1267; 6769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5605</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4582</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6734</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4783</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2406</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5605</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5451</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5329</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>8205</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3591; 12419</t>
+          <t>2739; 9871</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2164; 9907</t>
+          <t>2655; 10130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>555; 7028</t>
+          <t>2323; 10352</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1289; 7778</t>
+          <t>2095; 8558</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2650; 10197</t>
+          <t>3565; 11553</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2632; 9999</t>
+          <t>2151; 9890</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2160; 9776</t>
+          <t>561; 6450</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3072; 12514</t>
+          <t>1399; 7728</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7556; 18735</t>
+          <t>7860; 19279</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5919; 16067</t>
+          <t>5946; 16365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4161; 13203</t>
+          <t>4266; 13406</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5273; 16095</t>
+          <t>4642; 13457</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7942</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4809</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5536</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8734</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5166</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7942</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6348</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10627</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2698; 9884</t>
+          <t>2570; 8833</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2517; 9645</t>
+          <t>4430; 12443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4985; 13412</t>
+          <t>3429; 10441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2403; 10019</t>
+          <t>1984; 10153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2451; 9018</t>
+          <t>2854; 9500</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4216; 12766</t>
+          <t>2276; 10101</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3034; 11286</t>
+          <t>4981; 13516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1948; 10056</t>
+          <t>2582; 10920</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6627; 16191</t>
+          <t>6598; 15722</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8470; 19574</t>
+          <t>8728; 19749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10112; 21598</t>
+          <t>9598; 21358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6249; 17039</t>
+          <t>6027; 17509</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8998</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7691</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6279</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6193</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5310</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13742</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3062; 10644</t>
+          <t>5595; 13990</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3304; 10807</t>
+          <t>2851; 10345</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2668; 9490</t>
+          <t>2140; 8299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1452; 12613</t>
+          <t>3766; 13883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5266; 14489</t>
+          <t>3229; 10927</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2824; 9904</t>
+          <t>3273; 9926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2098; 8280</t>
+          <t>2184; 9032</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3438; 13218</t>
+          <t>2795; 11460</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10504; 22283</t>
+          <t>10508; 21196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7322; 17982</t>
+          <t>7453; 17716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5800; 15420</t>
+          <t>5462; 14879</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6507; 21811</t>
+          <t>7927; 20868</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12958; 26910</t>
+          <t>16713; 30782</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12225; 25543</t>
+          <t>13676; 27640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11815; 24797</t>
+          <t>12814; 25905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7779; 22522</t>
+          <t>11064; 25466</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16676; 31017</t>
+          <t>13711; 27978</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14124; 28594</t>
+          <t>11906; 25693</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12105; 25464</t>
+          <t>12002; 25156</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11891; 27497</t>
+          <t>9733; 23447</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>32995; 52511</t>
+          <t>34029; 53746</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28961; 47480</t>
+          <t>28283; 49257</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27336; 45555</t>
+          <t>27656; 49384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23828; 45074</t>
+          <t>23936; 42490</t>
         </is>
       </c>
     </row>
